--- a/Pipistrelli 2024.xlsx
+++ b/Pipistrelli 2024.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N129"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,11 @@
           <t>Provincia</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>provincia</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -551,6 +556,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -607,6 +617,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -663,6 +678,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -723,6 +743,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -778,7 +803,16 @@
       <c r="M6" t="n">
         <v>11.3434053</v>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -834,7 +868,16 @@
       <c r="M7" t="n">
         <v>11.3434053</v>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -895,6 +938,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -955,6 +1003,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1007,6 +1060,7 @@
         <v>12.0321866</v>
       </c>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1063,6 +1117,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1118,7 +1177,16 @@
       <c r="M12" t="n">
         <v>11.3017652</v>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1179,6 +1247,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1235,6 +1308,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1291,6 +1369,7 @@
         <v>11.5093217</v>
       </c>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1347,6 +1426,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1407,6 +1491,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1459,6 +1548,7 @@
         <v>11.5436596</v>
       </c>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1511,6 +1601,7 @@
         <v>11.5436596</v>
       </c>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1562,7 +1653,16 @@
       <c r="M20" t="n">
         <v>11.5356994</v>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1619,6 +1719,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1671,6 +1776,7 @@
         <v>12.0321866</v>
       </c>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1727,6 +1833,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1778,7 +1889,16 @@
       <c r="M24" t="n">
         <v>11.5844477</v>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1830,7 +1950,16 @@
       <c r="M25" t="n">
         <v>11.5844477</v>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1887,6 +2016,11 @@
           <t>VR</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>VR</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1945,6 +2079,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2001,6 +2140,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2056,7 +2200,16 @@
       <c r="M29" t="n">
         <v>11.5805788</v>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2113,6 +2266,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2164,7 +2322,16 @@
       <c r="M31" t="n">
         <v>11.4301268</v>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2218,7 +2385,16 @@
       <c r="M32" t="n">
         <v>11.6014322</v>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2270,7 +2446,16 @@
       <c r="M33" t="n">
         <v>11.5081895</v>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2329,6 +2514,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2384,7 +2574,16 @@
       <c r="M35" t="n">
         <v>11.7134998</v>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2440,7 +2639,16 @@
       <c r="M36" t="n">
         <v>11.7134998</v>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2497,6 +2705,11 @@
           <t>VR</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>VR</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2551,6 +2764,7 @@
         <v>11.5352125</v>
       </c>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2609,6 +2823,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2661,6 +2880,7 @@
         <v>11.6014322</v>
       </c>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2712,7 +2932,16 @@
       <c r="M41" t="n">
         <v>11.5831095</v>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2764,7 +2993,16 @@
       <c r="M42" t="n">
         <v>11.7291016</v>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -2825,6 +3063,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -2879,6 +3122,7 @@
         <v>11.6014322</v>
       </c>
       <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -2930,7 +3174,16 @@
       <c r="M45" t="n">
         <v>11.6526775</v>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -2982,7 +3235,16 @@
       <c r="M46" t="n">
         <v>11.4651626</v>
       </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3035,6 +3297,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -3093,6 +3360,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -3149,6 +3421,7 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -3207,6 +3480,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -3265,6 +3543,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -3321,6 +3604,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -3372,7 +3660,16 @@
       <c r="M53" t="n">
         <v>11.7041837</v>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -3431,6 +3728,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -3487,6 +3789,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -3547,6 +3854,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -3605,6 +3917,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -3663,6 +3980,11 @@
           <t>PD</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -3721,6 +4043,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -3775,6 +4102,7 @@
         <v>12.0321866</v>
       </c>
       <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -3826,7 +4154,16 @@
       <c r="M61" t="n">
         <v>11.3645426</v>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -3878,7 +4215,16 @@
       <c r="M62" t="n">
         <v>11.4431478</v>
       </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -3935,6 +4281,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -3986,7 +4337,16 @@
       <c r="M64" t="n">
         <v>11.4456338</v>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -4038,7 +4398,16 @@
       <c r="M65" t="n">
         <v>11.4456338</v>
       </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -4097,6 +4466,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -4148,7 +4522,16 @@
       <c r="M67" t="n">
         <v>11.6329987</v>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -4205,6 +4588,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -4256,7 +4644,16 @@
       <c r="M69" t="n">
         <v>11.5745789</v>
       </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -4313,6 +4710,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -4369,6 +4771,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -4425,6 +4832,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -4476,7 +4888,16 @@
       <c r="M73" t="n">
         <v>11.5356994</v>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -4533,6 +4954,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -4589,6 +5015,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -4640,7 +5071,16 @@
       <c r="M76" t="n">
         <v>9.745760000000001</v>
       </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -4694,7 +5134,16 @@
       <c r="M77" t="n">
         <v>11.4877438</v>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -4753,6 +5202,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -4804,7 +5258,16 @@
       <c r="M79" t="n">
         <v>11.4719785</v>
       </c>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -4856,7 +5319,16 @@
       <c r="M80" t="n">
         <v>11.6905167</v>
       </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -4908,7 +5380,16 @@
       <c r="M81" t="n">
         <v>11.5422153</v>
       </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -4962,7 +5443,16 @@
       <c r="M82" t="n">
         <v>11.3434053</v>
       </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -5018,7 +5508,16 @@
       <c r="M83" t="n">
         <v>11.5714548</v>
       </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -5077,6 +5576,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -5130,7 +5634,16 @@
       <c r="M85" t="n">
         <v>11.5733922</v>
       </c>
-      <c r="N85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -5182,7 +5695,16 @@
       <c r="M86" t="n">
         <v>11.6110489</v>
       </c>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -5239,6 +5761,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -5290,7 +5817,16 @@
       <c r="M88" t="n">
         <v>11.741934</v>
       </c>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -5347,6 +5883,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -5405,6 +5946,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -5461,6 +6007,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -5512,7 +6063,16 @@
       <c r="M92" t="n">
         <v>11.4583737</v>
       </c>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -5569,6 +6129,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -5627,6 +6192,7 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -5678,7 +6244,16 @@
       <c r="M95" t="n">
         <v>11.5121486</v>
       </c>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -5731,6 +6306,7 @@
         <v>11.576369</v>
       </c>
       <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -5787,6 +6363,7 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -5838,7 +6415,16 @@
       <c r="M98" t="n">
         <v>11.5097243</v>
       </c>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -5890,7 +6476,16 @@
       <c r="M99" t="n">
         <v>-1.5541362</v>
       </c>
-      <c r="N99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -5946,7 +6541,16 @@
       <c r="M100" t="n">
         <v>11.7583907</v>
       </c>
-      <c r="N100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -6003,6 +6607,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -6054,7 +6663,16 @@
       <c r="M102" t="n">
         <v>11.7321801</v>
       </c>
-      <c r="N102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -6111,6 +6729,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -6171,6 +6794,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -6229,6 +6857,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -6285,6 +6918,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -6336,7 +6974,16 @@
       <c r="M107" t="n">
         <v>11.5485978</v>
       </c>
-      <c r="N107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -6393,6 +7040,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -6444,7 +7096,16 @@
       <c r="M109" t="n">
         <v>11.5356994</v>
       </c>
-      <c r="N109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -6496,7 +7157,16 @@
       <c r="M110" t="n">
         <v>11.4422352</v>
       </c>
-      <c r="N110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -6557,6 +7227,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -6613,6 +7288,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -6669,6 +7349,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -6729,6 +7414,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -6777,6 +7467,7 @@
         <v>11.5551735</v>
       </c>
       <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -6828,7 +7519,16 @@
       <c r="M116" t="n">
         <v>11.5485978</v>
       </c>
-      <c r="N116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -6889,6 +7589,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -6944,7 +7649,16 @@
       <c r="M118" t="n">
         <v>11.584607</v>
       </c>
-      <c r="N118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -7005,6 +7719,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -7061,6 +7780,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -7112,7 +7836,16 @@
       <c r="M121" t="n">
         <v>11.5411704</v>
       </c>
-      <c r="N121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -7169,6 +7902,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -7220,7 +7958,16 @@
       <c r="M123" t="n">
         <v>11.38799</v>
       </c>
-      <c r="N123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -7281,6 +8028,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -7337,6 +8089,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -7397,6 +8154,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -7453,6 +8215,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -7508,7 +8275,16 @@
       <c r="M128" t="n">
         <v>11.5381176</v>
       </c>
-      <c r="N128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -7565,6 +8341,11 @@
         <v>11.5501458</v>
       </c>
       <c r="N129" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
         <is>
           <t>VI</t>
         </is>

--- a/Pipistrelli 2024.xlsx
+++ b/Pipistrelli 2024.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>vicenza</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cornedo Vicentino</t>
+          <t>Cornedo vicentino</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Altavilla Vicentina </t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bassano del Grappa </t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monticello Conte Otto</t>
+          <t>Monticello conte otto</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piovene Rocchette</t>
+          <t>Piovene rocchette</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>arcugnano</t>
+          <t>Arcugnano</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">montecchio </t>
+          <t>Montecchio maggiore</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2442,10 +2442,10 @@
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>42.663533</v>
+        <v>45.5479</v>
       </c>
       <c r="M34" t="n">
-        <v>12.286862</v>
+        <v>11.5446</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>VI</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Camisano Vicentino</t>
+          <t>Camisano vicentino</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Camisano Vicentino</t>
+          <t>Camisano vicentino</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pove del Grappa</t>
+          <t>Pove del grappa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thiene </t>
+          <t>Thiene</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tezze sul Brenta </t>
+          <t>Tezze sul brenta</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>altavilla vicentina</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>brogliano</t>
+          <t>Brogliano</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isola Vicentina </t>
+          <t>Isola vicentina</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>altavilla vicentina</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>vicenza</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>vicenza</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>45.443275</v>
+        <v>45.1332</v>
       </c>
       <c r="M76" t="n">
-        <v>9.745760000000001</v>
+        <v>10.0213</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>45.5208426</v>
+        <v>45.1332</v>
       </c>
       <c r="M80" t="n">
-        <v>11.6905167</v>
+        <v>10.0213</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Montecchio</t>
+          <t>Montecchio maggiore</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>VI</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Altavilla</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6182,6 +6182,11 @@
         <v>11.463433</v>
       </c>
       <c r="N97" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
@@ -6289,10 +6294,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>47.2186371</v>
+        <v>45.5479</v>
       </c>
       <c r="M99" t="n">
-        <v>-1.5541362</v>
+        <v>11.5446</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -6331,7 +6336,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Romano d'Ezzelino</t>
+          <t>Romano d'ezzelino</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6572,7 +6577,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bassano del Grappa </t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6631,7 +6636,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barbarano Mossano</t>
+          <t>Barbarano mossano</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7052,7 +7057,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7278,7 +7283,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dueville </t>
+          <t>Dueville</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7406,7 +7411,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Monticello Conte Otto</t>
+          <t>Monticello conte otto</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7470,7 +7475,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">

--- a/Pipistrelli 2024.xlsx
+++ b/Pipistrelli 2024.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cornedo vicentino</t>
+          <t>Cornedo Vicentino</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cornedo vicentino</t>
+          <t>Cornedo Vicentino</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grisignano </t>
+          <t>Grisignano Di Zocco</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1042,10 +1042,15 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.1821589</v>
+        <v>45.5479</v>
       </c>
       <c r="M10" t="n">
-        <v>12.0321866</v>
+        <v>11.5446</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1197,7 +1202,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1708,7 +1713,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grisignano</t>
+          <t>Grisignano Di Zocco</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1730,10 +1735,15 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>44.1821589</v>
+        <v>45.5479</v>
       </c>
       <c r="M22" t="n">
-        <v>12.0321866</v>
+        <v>11.5446</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2119,7 +2129,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monticello conte otto</t>
+          <t>Monticello Conte Otto</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2237,7 +2247,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piovene rocchette</t>
+          <t>Piovene Rocchette</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2417,7 +2427,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montecchio maggiore</t>
+          <t>Montecchio Maggiore</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2484,7 +2494,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Camisano vicentino</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2548,7 +2558,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Camisano vicentino</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2888,7 +2898,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pove del grappa</t>
+          <t>Pove Del Grappa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3122,7 +3132,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Isola vicentina</t>
+          <t>Isola Vicentina</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3534,7 +3544,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tezze sul brenta</t>
+          <t>Tezze Sul Brenta</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3778,7 +3788,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3964,7 +3974,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grisignano</t>
+          <t>Grisignano Di Zocco</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3989,10 +3999,15 @@
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>44.1821589</v>
+        <v>45.5479</v>
       </c>
       <c r="M60" t="n">
-        <v>12.0321866</v>
+        <v>11.5446</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4075,7 +4090,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Isola vicentina</t>
+          <t>Isola Vicentina</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4311,7 +4326,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4668,7 +4683,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4904,7 +4919,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Camisano</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4926,10 +4941,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>45.1332</v>
+        <v>45.5479</v>
       </c>
       <c r="M76" t="n">
-        <v>10.0213</v>
+        <v>11.5446</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -4938,7 +4953,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VI</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5161,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Camisano</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5168,10 +5183,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>45.1332</v>
+        <v>45.5479</v>
       </c>
       <c r="M80" t="n">
-        <v>10.0213</v>
+        <v>11.5446</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -5180,7 +5195,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VI</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5279,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cornedo vicentino</t>
+          <t>Cornedo Vicentino</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5632,7 +5647,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pove del grappa</t>
+          <t>Pove Del Grappa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5750,7 +5765,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Montecchio maggiore</t>
+          <t>Montecchio Maggiore</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5812,7 +5827,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5930,7 +5945,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6154,7 +6169,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6336,7 +6351,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Romano d'ezzelino</t>
+          <t>Romano D'Ezzelino</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6454,7 +6469,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pove del grappa</t>
+          <t>Pove Del Grappa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6577,7 +6592,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6636,7 +6651,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barbarano mossano</t>
+          <t>Barbarano Mossano</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7057,7 +7072,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7411,7 +7426,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Monticello conte otto</t>
+          <t>Monticello Conte Otto</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7475,7 +7490,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
